--- a/functions rodri/datos/PAR RPM.xlsx
+++ b/functions rodri/datos/PAR RPM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\OneDrive\Escritorio\ETECH\GitHub\ETR-Geometry\functions rodri\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\OneDrive\Escritorio\ETECH\GitHub\ETR-Geometry\functions rodri\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66E4257-C302-4AAB-9A26-D28A207D5160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA44DE5-C39B-431E-B375-DE07F13EC146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2430" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{646013F1-BC4C-476D-9A58-AE581D1795D8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{646013F1-BC4C-476D-9A58-AE581D1795D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/functions rodri/datos/PAR RPM.xlsx
+++ b/functions rodri/datos/PAR RPM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\OneDrive\Escritorio\ETECH\GitHub\ETR-Geometry\functions rodri\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA44DE5-C39B-431E-B375-DE07F13EC146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A636A6B0-8F62-4FC8-B896-6CA1817B6C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{646013F1-BC4C-476D-9A58-AE581D1795D8}"/>
   </bookViews>
@@ -413,10 +413,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4847898-DEF1-42A6-8E4D-D8B5D81E2E15}">
-  <dimension ref="A1:G685"/>
+  <dimension ref="A1:B685"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.90625" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -432,7 +433,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -440,7 +441,7 @@
         <v>12.356931104119852</v>
       </c>
       <c r="B3">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -448,7 +449,7 @@
         <v>19.792033717615695</v>
       </c>
       <c r="B4">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -456,7 +457,7 @@
         <v>24.818581963359364</v>
       </c>
       <c r="B5">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -464,7 +465,7 @@
         <v>29.740410453983372</v>
       </c>
       <c r="B6">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -472,7 +473,7 @@
         <v>34.766958699727041</v>
       </c>
       <c r="B7">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -480,7 +481,7 @@
         <v>39.68878719035105</v>
       </c>
       <c r="B8">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -488,7 +489,7 @@
         <v>42.202061313222885</v>
       </c>
       <c r="B9">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -496,7 +497,7 @@
         <v>47.123889803846893</v>
       </c>
       <c r="B10">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -504,7 +505,7 @@
         <v>52.045718294470902</v>
       </c>
       <c r="B11">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -512,7 +513,7 @@
         <v>57.072266540214571</v>
       </c>
       <c r="B12">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -520,7 +521,7 @@
         <v>61.994095030838579</v>
       </c>
       <c r="B13">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -528,7 +529,7 @@
         <v>66.915923521462588</v>
       </c>
       <c r="B14">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -536,7 +537,7 @@
         <v>71.942471767206257</v>
       </c>
       <c r="B15">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -544,7 +545,7 @@
         <v>76.864300257830266</v>
       </c>
       <c r="B16">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -552,7 +553,7 @@
         <v>81.890848503573935</v>
       </c>
       <c r="B17">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -560,7 +561,7 @@
         <v>86.812676994197943</v>
       </c>
       <c r="B18">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -568,7 +569,7 @@
         <v>91.734505484821952</v>
       </c>
       <c r="B19">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -576,7 +577,7 @@
         <v>96.761053730565621</v>
       </c>
       <c r="B20">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
@@ -584,7 +585,7 @@
         <v>99.169608098317795</v>
       </c>
       <c r="B21">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -592,7 +593,7 @@
         <v>101.68288222118963</v>
       </c>
       <c r="B22">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -600,7 +601,7 @@
         <v>106.81415022205296</v>
       </c>
       <c r="B23">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
@@ -608,7 +609,7 @@
         <v>108.90854532444615</v>
       </c>
       <c r="B24">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
@@ -616,7 +617,7 @@
         <v>112.05013797803595</v>
       </c>
       <c r="B25">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
@@ -624,7 +625,7 @@
         <v>114.14453308042914</v>
       </c>
       <c r="B26">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
@@ -632,7 +633,7 @@
         <v>116.23892818282233</v>
       </c>
       <c r="B27">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
@@ -640,7 +641,7 @@
         <v>121.47491593880532</v>
       </c>
       <c r="B28">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -648,7 +649,7 @@
         <v>123.56931104119852</v>
       </c>
       <c r="B29">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -656,7 +657,7 @@
         <v>126.71090369478831</v>
       </c>
       <c r="B30">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -664,7 +665,7 @@
         <v>131.94689145077132</v>
       </c>
       <c r="B31">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
@@ -672,7 +673,7 @@
         <v>136.1356816555577</v>
       </c>
       <c r="B32">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -680,7 +681,7 @@
         <v>141.37166941154069</v>
       </c>
       <c r="B33">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
@@ -688,7 +689,7 @@
         <v>146.60765716752368</v>
       </c>
       <c r="B34">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
@@ -696,7 +697,7 @@
         <v>150.79644737231007</v>
       </c>
       <c r="B35">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
@@ -704,7 +705,7 @@
         <v>159.17402778188284</v>
       </c>
       <c r="B36">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
@@ -712,7 +713,7 @@
         <v>163.36281798666923</v>
       </c>
       <c r="B37">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
@@ -720,7 +721,7 @@
         <v>170.69320084504542</v>
       </c>
       <c r="B38">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
@@ -728,7 +729,7 @@
         <v>179.0707812546182</v>
       </c>
       <c r="B39">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
@@ -736,7 +737,7 @@
         <v>183.25957145940458</v>
       </c>
       <c r="B40">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -744,7 +745,7 @@
         <v>188.49555921538757</v>
       </c>
       <c r="B41">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -752,7 +753,7 @@
         <v>193.73154697137056</v>
       </c>
       <c r="B42">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
@@ -760,7 +761,7 @@
         <v>197.92033717615695</v>
       </c>
       <c r="B43">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
@@ -768,7 +769,7 @@
         <v>206.29791758572975</v>
       </c>
       <c r="B44">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
@@ -776,7 +777,7 @@
         <v>210.48670779051614</v>
       </c>
       <c r="B45">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
@@ -784,7 +785,7 @@
         <v>215.72269554649912</v>
       </c>
       <c r="B46">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
@@ -792,7 +793,7 @@
         <v>220.95868330248211</v>
       </c>
       <c r="B47">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
@@ -800,7 +801,7 @@
         <v>226.1946710584651</v>
       </c>
       <c r="B48">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
@@ -808,7 +809,7 @@
         <v>230.38346126325149</v>
       </c>
       <c r="B49">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -816,7 +817,7 @@
         <v>235.61944901923448</v>
       </c>
       <c r="B50">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
@@ -824,7 +825,7 @@
         <v>240.85543677521747</v>
       </c>
       <c r="B51">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
@@ -832,7 +833,7 @@
         <v>245.04422698000386</v>
       </c>
       <c r="B52">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -840,7 +841,7 @@
         <v>250.28021473598685</v>
       </c>
       <c r="B53">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -848,7 +849,7 @@
         <v>255.51620249196984</v>
       </c>
       <c r="B54">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
@@ -856,7 +857,7 @@
         <v>260.7521902479528</v>
       </c>
       <c r="B55">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
@@ -864,7 +865,7 @@
         <v>264.94098045273921</v>
       </c>
       <c r="B56">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
@@ -872,7 +873,7 @@
         <v>270.1769682087222</v>
       </c>
       <c r="B57">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
@@ -880,7 +881,7 @@
         <v>275.41295596470519</v>
       </c>
       <c r="B58">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -888,7 +889,7 @@
         <v>280.64894372068818</v>
       </c>
       <c r="B59">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -896,7 +897,7 @@
         <v>284.83773392547454</v>
       </c>
       <c r="B60">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -904,7 +905,7 @@
         <v>290.07372168145753</v>
       </c>
       <c r="B61">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
@@ -912,7 +913,7 @@
         <v>295.30970943744052</v>
       </c>
       <c r="B62">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
@@ -920,7 +921,7 @@
         <v>300.54569719342351</v>
       </c>
       <c r="B63">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
@@ -928,7 +929,7 @@
         <v>304.73448739820992</v>
       </c>
       <c r="B64">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -936,7 +937,7 @@
         <v>309.97047515419291</v>
       </c>
       <c r="B65">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
@@ -944,7 +945,7 @@
         <v>315.2064629101759</v>
       </c>
       <c r="B66">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -952,7 +953,7 @@
         <v>320.44245066615889</v>
       </c>
       <c r="B67">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
@@ -960,7 +961,7 @@
         <v>324.63124087094525</v>
       </c>
       <c r="B68">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
@@ -968,7 +969,7 @@
         <v>329.86722862692824</v>
       </c>
       <c r="B69">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -976,7 +977,7 @@
         <v>337.19761148530444</v>
       </c>
       <c r="B70">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -984,7 +985,7 @@
         <v>342.43359924128742</v>
       </c>
       <c r="B71">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
@@ -992,7 +993,7 @@
         <v>347.66958699727041</v>
       </c>
       <c r="B72">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -1000,7 +1001,7 @@
         <v>351.85837720205683</v>
       </c>
       <c r="B73">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -1008,7 +1009,7 @@
         <v>357.09436495803982</v>
       </c>
       <c r="B74">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
@@ -1016,7 +1017,7 @@
         <v>362.33035271402281</v>
       </c>
       <c r="B75">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -1024,7 +1025,7 @@
         <v>364.42474781641596</v>
       </c>
       <c r="B76">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -1032,7 +1033,7 @@
         <v>371.75513067479216</v>
       </c>
       <c r="B77">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -1040,7 +1041,7 @@
         <v>379.08551353316835</v>
       </c>
       <c r="B78">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
@@ -1048,7 +1049,7 @@
         <v>384.32150128915134</v>
       </c>
       <c r="B79">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -1056,7 +1057,7 @@
         <v>389.55748904513433</v>
       </c>
       <c r="B80">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -1064,7 +1065,7 @@
         <v>394.79347680111732</v>
       </c>
       <c r="B81">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -1072,7 +1073,7 @@
         <v>398.98226700590374</v>
       </c>
       <c r="B82">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -1080,7 +1081,7 @@
         <v>404.21825476188667</v>
       </c>
       <c r="B83">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -1088,7 +1089,7 @@
         <v>409.45424251786966</v>
       </c>
       <c r="B84">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -1096,7 +1097,7 @@
         <v>414.69023027385265</v>
       </c>
       <c r="B85">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -1104,7 +1105,7 @@
         <v>418.87902047863906</v>
       </c>
       <c r="B86">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -1112,7 +1113,7 @@
         <v>424.11500823462205</v>
       </c>
       <c r="B87">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -1120,7 +1121,7 @@
         <v>429.35099599060504</v>
       </c>
       <c r="B88">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -1128,7 +1129,7 @@
         <v>433.53978619539146</v>
       </c>
       <c r="B89">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -1136,7 +1137,7 @@
         <v>438.77577395137445</v>
       </c>
       <c r="B90">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -1144,7 +1145,7 @@
         <v>444.01176170735738</v>
       </c>
       <c r="B91">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -1152,7 +1153,7 @@
         <v>449.24774946334037</v>
       </c>
       <c r="B92">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -1160,7 +1161,7 @@
         <v>453.43653966812678</v>
       </c>
       <c r="B93">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -1168,7 +1169,7 @@
         <v>458.67252742410977</v>
       </c>
       <c r="B94">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -1176,7 +1177,7 @@
         <v>463.90851518009276</v>
       </c>
       <c r="B95">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -1184,7 +1185,7 @@
         <v>469.14450293607575</v>
       </c>
       <c r="B96">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -1192,7 +1193,7 @@
         <v>473.33329314086217</v>
       </c>
       <c r="B97">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -1200,7 +1201,7 @@
         <v>478.56928089684516</v>
       </c>
       <c r="B98">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -1208,7 +1209,7 @@
         <v>483.80526865282809</v>
       </c>
       <c r="B99">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -1216,7 +1217,7 @@
         <v>491.13565151120429</v>
       </c>
       <c r="B100">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -1224,7 +1225,7 @@
         <v>496.37163926718728</v>
       </c>
       <c r="B101">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -1232,7 +1233,7 @@
         <v>500.56042947197369</v>
       </c>
       <c r="B102">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -1240,7 +1241,7 @@
         <v>505.79641722795668</v>
       </c>
       <c r="B103">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -1248,7 +1249,7 @@
         <v>511.03240498393967</v>
       </c>
       <c r="B104">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -1256,7 +1257,7 @@
         <v>516.26839273992266</v>
       </c>
       <c r="B105">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -1264,7 +1265,7 @@
         <v>523.59877559829886</v>
       </c>
       <c r="B106">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -1272,7 +1273,7 @@
         <v>530.92915845667505</v>
       </c>
       <c r="B107">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -1280,7 +1281,7 @@
         <v>538.25954131505125</v>
       </c>
       <c r="B108">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
@@ -1288,7 +1289,7 @@
         <v>545.58992417342733</v>
       </c>
       <c r="B109">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -1296,7 +1297,7 @@
         <v>547.6843192758206</v>
       </c>
       <c r="B110">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -1304,7 +1305,7 @@
         <v>552.92030703180353</v>
       </c>
       <c r="B111">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -1312,7 +1313,7 @@
         <v>558.15629478778658</v>
       </c>
       <c r="B112">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -1320,7 +1321,7 @@
         <v>563.39228254376951</v>
       </c>
       <c r="B113">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -1328,7 +1329,7 @@
         <v>567.58107274855593</v>
       </c>
       <c r="B114">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -1336,7 +1337,7 @@
         <v>572.81706050453897</v>
       </c>
       <c r="B115">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -1344,7 +1345,7 @@
         <v>578.0530482605219</v>
       </c>
       <c r="B116">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -1352,7 +1353,7 @@
         <v>583.28903601650495</v>
       </c>
       <c r="B117">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -1360,7 +1361,7 @@
         <v>587.47782622129125</v>
       </c>
       <c r="B118">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -1368,7 +1369,7 @@
         <v>592.7138139772743</v>
       </c>
       <c r="B119">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -1376,7 +1377,7 @@
         <v>597.94980173325723</v>
       </c>
       <c r="B120">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -1384,7 +1385,7 @@
         <v>603.18578948924028</v>
       </c>
       <c r="B121">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -1392,7 +1393,7 @@
         <v>607.37457969402669</v>
       </c>
       <c r="B122">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -1400,7 +1401,7 @@
         <v>612.61056745000963</v>
       </c>
       <c r="B123">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -1408,7 +1409,7 @@
         <v>617.84655520599267</v>
       </c>
       <c r="B124">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -1416,7 +1417,7 @@
         <v>625.17693806436876</v>
       </c>
       <c r="B125">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -1424,7 +1425,7 @@
         <v>632.50732092274495</v>
       </c>
       <c r="B126">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -1432,7 +1433,7 @@
         <v>637.743308678728</v>
       </c>
       <c r="B127">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -1440,7 +1441,7 @@
         <v>639.83770378112115</v>
       </c>
       <c r="B128">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -1448,7 +1449,7 @@
         <v>647.16808663949735</v>
       </c>
       <c r="B129">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -1456,7 +1457,7 @@
         <v>654.49846949787354</v>
       </c>
       <c r="B130">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -1464,7 +1465,7 @@
         <v>659.73445725385648</v>
       </c>
       <c r="B131">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -1472,7 +1473,7 @@
         <v>664.97044500983952</v>
       </c>
       <c r="B132">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -1480,7 +1481,7 @@
         <v>669.15923521462594</v>
       </c>
       <c r="B133">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -1488,7 +1489,7 @@
         <v>674.39522297060887</v>
       </c>
       <c r="B134">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -1496,7 +1497,7 @@
         <v>681.72560582898507</v>
       </c>
       <c r="B135">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -1504,7 +1505,7 @@
         <v>686.96159358496811</v>
       </c>
       <c r="B136">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -1512,7 +1513,7 @@
         <v>692.19758134095105</v>
       </c>
       <c r="B137">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -1520,7 +1521,7 @@
         <v>697.43356909693409</v>
       </c>
       <c r="B138">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -1528,7 +1529,7 @@
         <v>699.52796419932724</v>
       </c>
       <c r="B139">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -1536,7 +1537,7 @@
         <v>701.62235930172039</v>
       </c>
       <c r="B140">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -1544,7 +1545,7 @@
         <v>706.85834705770344</v>
       </c>
       <c r="B141">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -1552,7 +1553,7 @@
         <v>712.09433481368637</v>
       </c>
       <c r="B142">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -1560,7 +1561,7 @@
         <v>714.18872991607964</v>
       </c>
       <c r="B143">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -1568,7 +1569,7 @@
         <v>716.28312501847279</v>
       </c>
       <c r="B144">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -1576,7 +1577,7 @@
         <v>719.42471767206257</v>
       </c>
       <c r="B145">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -1584,7 +1585,7 @@
         <v>721.51911277445583</v>
       </c>
       <c r="B146">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -1592,7 +1593,7 @@
         <v>724.66070542804562</v>
       </c>
       <c r="B147">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -1600,7 +1601,7 @@
         <v>726.75510053043877</v>
       </c>
       <c r="B148">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -1608,7 +1609,7 @@
         <v>728.84949563283192</v>
       </c>
       <c r="B149">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -1616,7 +1617,7 @@
         <v>731.99108828642181</v>
       </c>
       <c r="B150">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -1624,7 +1625,7 @@
         <v>734.08548338881496</v>
       </c>
       <c r="B151">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -1632,7 +1633,7 @@
         <v>736.17987849120811</v>
       </c>
       <c r="B152">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -1640,7 +1641,7 @@
         <v>739.3214711447979</v>
       </c>
       <c r="B153">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -1648,7 +1649,7 @@
         <v>741.41586624719116</v>
       </c>
       <c r="B154">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -1656,7 +1657,7 @@
         <v>744.55745890078094</v>
       </c>
       <c r="B155">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -1664,7 +1665,7 @@
         <v>746.65185400317409</v>
       </c>
       <c r="B156">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -1672,7 +1673,7 @@
         <v>748.74624910556736</v>
       </c>
       <c r="B157">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -1680,7 +1681,7 @@
         <v>751.88784175915714</v>
       </c>
       <c r="B158">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -1688,7 +1689,7 @@
         <v>753.98223686155029</v>
       </c>
       <c r="B159">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -1696,7 +1697,7 @@
         <v>756.07663196394356</v>
       </c>
       <c r="B160">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -1704,7 +1705,7 @@
         <v>759.21822461753334</v>
       </c>
       <c r="B161">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -1712,7 +1713,7 @@
         <v>761.31261971992649</v>
       </c>
       <c r="B162">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -1720,7 +1721,7 @@
         <v>763.40701482231964</v>
       </c>
       <c r="B163">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -1728,7 +1729,7 @@
         <v>766.54860747590953</v>
       </c>
       <c r="B164">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -1736,7 +1737,7 @@
         <v>768.64300257830268</v>
       </c>
       <c r="B165">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -1744,7 +1745,7 @@
         <v>771.78459523189247</v>
       </c>
       <c r="B166">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -1752,7 +1753,7 @@
         <v>773.87899033428562</v>
       </c>
       <c r="B167">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -1760,7 +1761,7 @@
         <v>775.97338543667888</v>
       </c>
       <c r="B168">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -1768,7 +1769,7 @@
         <v>779.11497809026866</v>
       </c>
       <c r="B169">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -1776,7 +1777,7 @@
         <v>781.20937319266181</v>
       </c>
       <c r="B170">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -1784,7 +1785,7 @@
         <v>786.44536094864486</v>
       </c>
       <c r="B171">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -1792,7 +1793,7 @@
         <v>788.53975605103801</v>
       </c>
       <c r="B172">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -1800,7 +1801,7 @@
         <v>791.68134870462779</v>
       </c>
       <c r="B173">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -1808,7 +1809,7 @@
         <v>793.77574380702106</v>
       </c>
       <c r="B174">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -1816,7 +1817,7 @@
         <v>795.87013890941421</v>
       </c>
       <c r="B175">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -1824,7 +1825,7 @@
         <v>799.01173156300399</v>
       </c>
       <c r="B176">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -1832,7 +1833,7 @@
         <v>801.10612666539726</v>
       </c>
       <c r="B177">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -1840,7 +1841,7 @@
         <v>803.20052176779041</v>
       </c>
       <c r="B178">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -1848,7 +1849,7 @@
         <v>806.34211442138019</v>
       </c>
       <c r="B179">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -1856,7 +1857,7 @@
         <v>808.43650952377334</v>
       </c>
       <c r="B180">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -1864,7 +1865,7 @@
         <v>810.5309046261666</v>
       </c>
       <c r="B181">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -1872,7 +1873,7 @@
         <v>813.67249727975639</v>
       </c>
       <c r="B182">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -1880,7 +1881,7 @@
         <v>815.76689238214954</v>
       </c>
       <c r="B183">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -1888,7 +1889,7 @@
         <v>818.90848503573932</v>
       </c>
       <c r="B184">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -1896,7 +1897,7 @@
         <v>821.00288013813258</v>
       </c>
       <c r="B185">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -1904,7 +1905,7 @@
         <v>823.09727524052573</v>
       </c>
       <c r="B186">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -1912,7 +1913,7 @@
         <v>826.23886789411551</v>
       </c>
       <c r="B187">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -1920,7 +1921,7 @@
         <v>830.42765809890193</v>
       </c>
       <c r="B188">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -1928,7 +1929,7 @@
         <v>835.66364585488498</v>
       </c>
       <c r="B189">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -1936,7 +1937,7 @@
         <v>842.99402871326106</v>
       </c>
       <c r="B190">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -1944,7 +1945,7 @@
         <v>848.23001646924411</v>
       </c>
       <c r="B191">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -1952,7 +1953,7 @@
         <v>853.46600422522704</v>
       </c>
       <c r="B192">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -1960,7 +1961,7 @@
         <v>857.65479443001345</v>
       </c>
       <c r="B193">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -1968,7 +1969,7 @@
         <v>862.8907821859965</v>
       </c>
       <c r="B194">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -1976,7 +1977,7 @@
         <v>868.12676994197943</v>
       </c>
       <c r="B195">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -1984,7 +1985,7 @@
         <v>873.36275769796248</v>
       </c>
       <c r="B196">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -1992,7 +1993,7 @@
         <v>877.55154790274889</v>
       </c>
       <c r="B197">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -2000,7 +2001,7 @@
         <v>882.78753565873183</v>
       </c>
       <c r="B198">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -2008,7 +2009,7 @@
         <v>888.02352341471476</v>
       </c>
       <c r="B199">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -2016,7 +2017,7 @@
         <v>890.11791851710802</v>
       </c>
       <c r="B200">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -2024,7 +2025,7 @@
         <v>893.25951117069781</v>
       </c>
       <c r="B201">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -2032,7 +2033,7 @@
         <v>895.35390627309096</v>
       </c>
       <c r="B202">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -2040,7 +2041,7 @@
         <v>897.44830137548422</v>
       </c>
       <c r="B203">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -2048,7 +2049,7 @@
         <v>900.589894029074</v>
       </c>
       <c r="B204">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -2056,7 +2057,7 @@
         <v>902.68428913146715</v>
       </c>
       <c r="B205">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -2064,7 +2065,7 @@
         <v>904.77868423386042</v>
       </c>
       <c r="B206">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -2072,7 +2073,7 @@
         <v>907.9202768874502</v>
       </c>
       <c r="B207">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -2080,7 +2081,7 @@
         <v>910.01467198984335</v>
       </c>
       <c r="B208">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -2088,7 +2089,7 @@
         <v>913.15626464343313</v>
       </c>
       <c r="B209">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -2096,7 +2097,7 @@
         <v>915.2506597458264</v>
       </c>
       <c r="B210">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -2104,7 +2105,7 @@
         <v>917.34505484821955</v>
       </c>
       <c r="B211">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -2112,7 +2113,7 @@
         <v>920.48664750180933</v>
       </c>
       <c r="B212">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -2120,7 +2121,7 @@
         <v>922.58104260420259</v>
       </c>
       <c r="B213">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -2128,7 +2129,7 @@
         <v>924.67543770659574</v>
       </c>
       <c r="B214">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -2136,7 +2137,7 @@
         <v>927.81703036018553</v>
       </c>
       <c r="B215">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -2144,7 +2145,7 @@
         <v>929.91142546257868</v>
       </c>
       <c r="B216">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -2152,7 +2153,7 @@
         <v>933.05301811616846</v>
       </c>
       <c r="B217">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -2160,7 +2161,7 @@
         <v>935.14741321856172</v>
       </c>
       <c r="B218">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -2168,7 +2169,7 @@
         <v>937.24180832095487</v>
       </c>
       <c r="B219">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -2176,7 +2177,7 @@
         <v>940.38340097454466</v>
       </c>
       <c r="B220">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -2184,7 +2185,7 @@
         <v>944.57219117933107</v>
       </c>
       <c r="B221">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -2192,7 +2193,7 @@
         <v>947.71378383292085</v>
       </c>
       <c r="B222">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -2200,7 +2201,7 @@
         <v>949.80817893531412</v>
       </c>
       <c r="B223">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -2208,7 +2209,7 @@
         <v>955.04416669129705</v>
       </c>
       <c r="B224">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -2216,7 +2217,7 @@
         <v>960.2801544472801</v>
       </c>
       <c r="B225">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -2224,7 +2225,7 @@
         <v>964.4689446520664</v>
       </c>
       <c r="B226">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -2232,7 +2233,7 @@
         <v>969.70493240804944</v>
       </c>
       <c r="B227">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -2240,7 +2241,7 @@
         <v>974.94092016403238</v>
       </c>
       <c r="B228">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -2248,7 +2249,7 @@
         <v>980.17690792001542</v>
       </c>
       <c r="B229">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -2256,7 +2257,7 @@
         <v>982.27130302240857</v>
       </c>
       <c r="B230">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -2264,7 +2265,7 @@
         <v>984.36569812480184</v>
       </c>
       <c r="B231">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -2272,7 +2273,7 @@
         <v>989.60168588078477</v>
       </c>
       <c r="B232">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -2280,7 +2281,7 @@
         <v>994.83767363676782</v>
       </c>
       <c r="B233">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -2288,7 +2289,7 @@
         <v>999.02646384155412</v>
       </c>
       <c r="B234">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -2296,7 +2297,7 @@
         <v>1004.2624515975372</v>
       </c>
       <c r="B235">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -2304,7 +2305,7 @@
         <v>1011.5928344559134</v>
       </c>
       <c r="B236">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -2312,7 +2313,7 @@
         <v>1016.8288222118963</v>
       </c>
       <c r="B237">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -2320,7 +2321,7 @@
         <v>1022.0648099678793</v>
       </c>
       <c r="B238">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -2328,7 +2329,7 @@
         <v>1027.3007977238624</v>
       </c>
       <c r="B239">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -2336,7 +2337,7 @@
         <v>1031.4895879286487</v>
       </c>
       <c r="B240">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -2344,7 +2345,7 @@
         <v>1036.7255756846316</v>
       </c>
       <c r="B241">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -2352,7 +2353,7 @@
         <v>1038.8199707870249</v>
       </c>
       <c r="B242">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -2360,7 +2361,7 @@
         <v>1046.1503536454011</v>
       </c>
       <c r="B243">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -2368,7 +2369,7 @@
         <v>1057.6695267085636</v>
       </c>
       <c r="B244">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -2376,7 +2377,7 @@
         <v>1057.6695267085636</v>
       </c>
       <c r="B245">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -2384,7 +2385,7 @@
         <v>1068.1415022205297</v>
       </c>
       <c r="B246">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -2392,7 +2393,7 @@
         <v>1078.6134777324955</v>
       </c>
       <c r="B247">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -2400,7 +2401,7 @@
         <v>1078.6134777324955</v>
       </c>
       <c r="B248">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -2408,7 +2409,7 @@
         <v>1089.0854532444616</v>
       </c>
       <c r="B249">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -2416,7 +2417,7 @@
         <v>1089.0854532444616</v>
       </c>
       <c r="B250">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -2424,7 +2425,7 @@
         <v>1089.0854532444616</v>
       </c>
       <c r="B251">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -2432,7 +2433,7 @@
         <v>1099.5574287564275</v>
       </c>
       <c r="B252">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -2440,7 +2441,7 @@
         <v>1110.0294042683936</v>
       </c>
       <c r="B253">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -2448,7 +2449,7 @@
         <v>1110.0294042683936</v>
       </c>
       <c r="B254">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -2456,7 +2457,7 @@
         <v>1120.5013797803595</v>
       </c>
       <c r="B255">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -2464,7 +2465,7 @@
         <v>1120.5013797803595</v>
       </c>
       <c r="B256">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -2472,7 +2473,7 @@
         <v>1130.9733552923256</v>
       </c>
       <c r="B257">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -2480,7 +2481,7 @@
         <v>1130.9733552923256</v>
       </c>
       <c r="B258">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -2488,7 +2489,7 @@
         <v>1141.4453308042914</v>
       </c>
       <c r="B259">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -2496,7 +2497,7 @@
         <v>1141.4453308042914</v>
       </c>
       <c r="B260">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -2504,7 +2505,7 @@
         <v>1151.9173063162575</v>
       </c>
       <c r="B261">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -2512,7 +2513,7 @@
         <v>1151.9173063162575</v>
       </c>
       <c r="B262">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -2520,7 +2521,7 @@
         <v>1162.3892818282234</v>
       </c>
       <c r="B263">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -2528,7 +2529,7 @@
         <v>1162.3892818282234</v>
       </c>
       <c r="B264">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -2536,7 +2537,7 @@
         <v>1172.8612573401895</v>
       </c>
       <c r="B265">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -2544,7 +2545,7 @@
         <v>1172.8612573401895</v>
       </c>
       <c r="B266">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -2552,7 +2553,7 @@
         <v>1183.3332328521553</v>
       </c>
       <c r="B267">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -2560,7 +2561,7 @@
         <v>1183.3332328521553</v>
       </c>
       <c r="B268">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -2568,7 +2569,7 @@
         <v>1193.8052083641214</v>
       </c>
       <c r="B269">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -2576,7 +2577,7 @@
         <v>1193.8052083641214</v>
       </c>
       <c r="B270">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -2584,7 +2585,7 @@
         <v>1193.8052083641214</v>
       </c>
       <c r="B271">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -2592,7 +2593,7 @@
         <v>1204.2771838760873</v>
       </c>
       <c r="B272">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -2600,7 +2601,7 @@
         <v>1204.2771838760873</v>
       </c>
       <c r="B273">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -2608,7 +2609,7 @@
         <v>1214.7491593880534</v>
       </c>
       <c r="B274">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -2616,7 +2617,7 @@
         <v>1214.7491593880534</v>
       </c>
       <c r="B275">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -2624,7 +2625,7 @@
         <v>1225.2211349000193</v>
       </c>
       <c r="B276">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -2632,7 +2633,7 @@
         <v>1225.2211349000193</v>
       </c>
       <c r="B277">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -2640,7 +2641,7 @@
         <v>1235.6931104119853</v>
       </c>
       <c r="B278">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -2648,7 +2649,7 @@
         <v>1235.6931104119853</v>
       </c>
       <c r="B279">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -2656,7 +2657,7 @@
         <v>1246.1650859239512</v>
       </c>
       <c r="B280">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -2664,7 +2665,7 @@
         <v>1246.1650859239512</v>
       </c>
       <c r="B281">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -2672,7 +2673,7 @@
         <v>1246.1650859239512</v>
       </c>
       <c r="B282">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -2680,7 +2681,7 @@
         <v>1256.6370614359173</v>
       </c>
       <c r="B283">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -2688,7 +2689,7 @@
         <v>1256.6370614359173</v>
       </c>
       <c r="B284">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -2696,7 +2697,7 @@
         <v>1256.6370614359173</v>
       </c>
       <c r="B285">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -2704,7 +2705,7 @@
         <v>1267.1090369478832</v>
       </c>
       <c r="B286">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -2712,7 +2713,7 @@
         <v>1267.1090369478832</v>
       </c>
       <c r="B287">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -2720,7 +2721,7 @@
         <v>1267.1090369478832</v>
       </c>
       <c r="B288">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -2728,7 +2729,7 @@
         <v>1277.581012459849</v>
       </c>
       <c r="B289">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -2736,7 +2737,7 @@
         <v>1277.581012459849</v>
       </c>
       <c r="B290">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -2744,7 +2745,7 @@
         <v>1277.581012459849</v>
       </c>
       <c r="B291">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -2752,7 +2753,7 @@
         <v>1277.581012459849</v>
       </c>
       <c r="B292">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -2760,7 +2761,7 @@
         <v>1288.0529879718151</v>
       </c>
       <c r="B293">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -2768,7 +2769,7 @@
         <v>1288.0529879718151</v>
       </c>
       <c r="B294">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -2776,7 +2777,7 @@
         <v>1298.524963483781</v>
       </c>
       <c r="B295">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -2784,7 +2785,7 @@
         <v>1298.524963483781</v>
       </c>
       <c r="B296">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -2792,7 +2793,7 @@
         <v>1308.9969389957471</v>
       </c>
       <c r="B297">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -2800,7 +2801,7 @@
         <v>1319.468914507713</v>
       </c>
       <c r="B298">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -2808,7 +2809,7 @@
         <v>1319.468914507713</v>
       </c>
       <c r="B299">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -2816,7 +2817,7 @@
         <v>1329.940890019679</v>
       </c>
       <c r="B300">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -2824,7 +2825,7 @@
         <v>1329.940890019679</v>
       </c>
       <c r="B301">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -2832,7 +2833,7 @@
         <v>1340.4128655316449</v>
       </c>
       <c r="B302">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -2840,7 +2841,7 @@
         <v>1340.4128655316449</v>
       </c>
       <c r="B303">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -2848,7 +2849,7 @@
         <v>1350.884841043611</v>
       </c>
       <c r="B304">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -2856,7 +2857,7 @@
         <v>1361.3568165555769</v>
       </c>
       <c r="B305">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -2864,7 +2865,7 @@
         <v>1361.3568165555769</v>
       </c>
       <c r="B306">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -2872,7 +2873,7 @@
         <v>1361.3568165555769</v>
       </c>
       <c r="B307">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -2880,7 +2881,7 @@
         <v>1371.828792067543</v>
       </c>
       <c r="B308">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -2888,7 +2889,7 @@
         <v>1371.828792067543</v>
       </c>
       <c r="B309">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -2896,7 +2897,7 @@
         <v>1382.3007675795088</v>
       </c>
       <c r="B310">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -2904,7 +2905,7 @@
         <v>1382.3007675795088</v>
       </c>
       <c r="B311">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -2912,7 +2913,7 @@
         <v>1392.7727430914749</v>
       </c>
       <c r="B312">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -2920,7 +2921,7 @@
         <v>1392.7727430914749</v>
       </c>
       <c r="B313">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -2928,7 +2929,7 @@
         <v>1403.2447186034408</v>
       </c>
       <c r="B314">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -2936,7 +2937,7 @@
         <v>1403.2447186034408</v>
       </c>
       <c r="B315">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
@@ -2944,7 +2945,7 @@
         <v>1413.7166941154069</v>
       </c>
       <c r="B316">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
@@ -2952,7 +2953,7 @@
         <v>1413.7166941154069</v>
       </c>
       <c r="B317">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
@@ -2960,7 +2961,7 @@
         <v>1424.1886696273727</v>
       </c>
       <c r="B318">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
@@ -2968,7 +2969,7 @@
         <v>1424.1886696273727</v>
       </c>
       <c r="B319">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
@@ -2976,7 +2977,7 @@
         <v>1434.6606451393388</v>
       </c>
       <c r="B320">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
@@ -2984,7 +2985,7 @@
         <v>1434.6606451393388</v>
       </c>
       <c r="B321">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
@@ -2992,7 +2993,7 @@
         <v>1445.1326206513047</v>
       </c>
       <c r="B322">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -3000,7 +3001,7 @@
         <v>1445.1326206513047</v>
       </c>
       <c r="B323">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -3008,7 +3009,7 @@
         <v>1455.6045961632708</v>
       </c>
       <c r="B324">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -3016,7 +3017,7 @@
         <v>1455.6045961632708</v>
       </c>
       <c r="B325">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -3024,7 +3025,7 @@
         <v>1466.0765716752367</v>
       </c>
       <c r="B326">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
@@ -3032,7 +3033,7 @@
         <v>1466.0765716752367</v>
       </c>
       <c r="B327">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
@@ -3040,7 +3041,7 @@
         <v>1476.5485471872028</v>
       </c>
       <c r="B328">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -3048,7 +3049,7 @@
         <v>1476.5485471872028</v>
       </c>
       <c r="B329">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -3056,7 +3057,7 @@
         <v>1487.0205226991686</v>
       </c>
       <c r="B330">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -3064,7 +3065,7 @@
         <v>1497.4924982111347</v>
       </c>
       <c r="B331">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -3072,7 +3073,7 @@
         <v>1497.4924982111347</v>
       </c>
       <c r="B332">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -3080,7 +3081,7 @@
         <v>1497.4924982111347</v>
       </c>
       <c r="B333">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
@@ -3088,7 +3089,7 @@
         <v>1507.9644737231006</v>
       </c>
       <c r="B334">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
@@ -3096,7 +3097,7 @@
         <v>1507.9644737231006</v>
       </c>
       <c r="B335">
-        <v>27.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
@@ -4899,7 +4900,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561">
         <v>1822.12373908208</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562">
         <v>1822.12373908208</v>
       </c>
@@ -4915,7 +4916,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563">
         <v>1822.12373908208</v>
       </c>
@@ -4923,7 +4924,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564">
         <v>1822.12373908208</v>
       </c>
@@ -4931,7 +4932,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565">
         <v>1832.5957145940458</v>
       </c>
@@ -4939,7 +4940,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566">
         <v>1832.5957145940458</v>
       </c>
@@ -4947,7 +4948,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567">
         <v>1832.5957145940458</v>
       </c>
@@ -4955,7 +4956,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568">
         <v>1832.5957145940458</v>
       </c>
@@ -4963,7 +4964,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569">
         <v>1832.5957145940458</v>
       </c>
@@ -4971,7 +4972,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570">
         <v>1832.5957145940458</v>
       </c>
@@ -4979,7 +4980,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571">
         <v>1843.0676901060119</v>
       </c>
@@ -4987,7 +4988,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572">
         <v>1843.0676901060119</v>
       </c>
@@ -4995,7 +4996,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573">
         <v>1843.0676901060119</v>
       </c>
@@ -5003,7 +5004,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574">
         <v>1843.0676901060119</v>
       </c>
@@ -5011,7 +5012,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575">
         <v>1843.0676901060119</v>
       </c>
@@ -5019,16 +5020,12 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576">
         <v>1843.0676901060119</v>
       </c>
       <c r="B576">
         <v>10.3</v>
-      </c>
-      <c r="G576">
-        <f>16*0.0254/2</f>
-        <v>0.20319999999999999</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">

--- a/functions rodri/datos/PAR RPM.xlsx
+++ b/functions rodri/datos/PAR RPM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\OneDrive\Escritorio\ETECH\GitHub\ETR-Geometry\functions rodri\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A636A6B0-8F62-4FC8-B896-6CA1817B6C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1B603A-47D5-4FCD-9036-2BF3965BC274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{646013F1-BC4C-476D-9A58-AE581D1795D8}"/>
   </bookViews>
@@ -2705,7 +2705,7 @@
         <v>1267.1090369478832</v>
       </c>
       <c r="B286">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -2713,7 +2713,7 @@
         <v>1267.1090369478832</v>
       </c>
       <c r="B287">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -2721,7 +2721,7 @@
         <v>1267.1090369478832</v>
       </c>
       <c r="B288">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -2729,7 +2729,7 @@
         <v>1277.581012459849</v>
       </c>
       <c r="B289">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -2737,7 +2737,7 @@
         <v>1277.581012459849</v>
       </c>
       <c r="B290">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -2745,7 +2745,7 @@
         <v>1277.581012459849</v>
       </c>
       <c r="B291">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -2753,7 +2753,7 @@
         <v>1277.581012459849</v>
       </c>
       <c r="B292">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -2761,7 +2761,7 @@
         <v>1288.0529879718151</v>
       </c>
       <c r="B293">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -2769,7 +2769,7 @@
         <v>1288.0529879718151</v>
       </c>
       <c r="B294">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -2777,7 +2777,7 @@
         <v>1298.524963483781</v>
       </c>
       <c r="B295">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -2785,7 +2785,7 @@
         <v>1298.524963483781</v>
       </c>
       <c r="B296">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -2793,7 +2793,7 @@
         <v>1308.9969389957471</v>
       </c>
       <c r="B297">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -2801,7 +2801,7 @@
         <v>1319.468914507713</v>
       </c>
       <c r="B298">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -2809,7 +2809,7 @@
         <v>1319.468914507713</v>
       </c>
       <c r="B299">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -2817,7 +2817,7 @@
         <v>1329.940890019679</v>
       </c>
       <c r="B300">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -2825,7 +2825,7 @@
         <v>1329.940890019679</v>
       </c>
       <c r="B301">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -2833,7 +2833,7 @@
         <v>1340.4128655316449</v>
       </c>
       <c r="B302">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -2841,7 +2841,7 @@
         <v>1340.4128655316449</v>
       </c>
       <c r="B303">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -2849,7 +2849,7 @@
         <v>1350.884841043611</v>
       </c>
       <c r="B304">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -2857,7 +2857,7 @@
         <v>1361.3568165555769</v>
       </c>
       <c r="B305">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -2865,7 +2865,7 @@
         <v>1361.3568165555769</v>
       </c>
       <c r="B306">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -2873,7 +2873,7 @@
         <v>1361.3568165555769</v>
       </c>
       <c r="B307">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -2881,7 +2881,7 @@
         <v>1371.828792067543</v>
       </c>
       <c r="B308">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -2889,7 +2889,7 @@
         <v>1371.828792067543</v>
       </c>
       <c r="B309">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -2897,7 +2897,7 @@
         <v>1382.3007675795088</v>
       </c>
       <c r="B310">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -2905,7 +2905,7 @@
         <v>1382.3007675795088</v>
       </c>
       <c r="B311">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -2913,7 +2913,7 @@
         <v>1392.7727430914749</v>
       </c>
       <c r="B312">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -2921,7 +2921,7 @@
         <v>1392.7727430914749</v>
       </c>
       <c r="B313">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -2929,7 +2929,7 @@
         <v>1403.2447186034408</v>
       </c>
       <c r="B314">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -2937,7 +2937,7 @@
         <v>1403.2447186034408</v>
       </c>
       <c r="B315">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
@@ -2945,7 +2945,7 @@
         <v>1413.7166941154069</v>
       </c>
       <c r="B316">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
@@ -2953,7 +2953,7 @@
         <v>1413.7166941154069</v>
       </c>
       <c r="B317">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
@@ -2961,7 +2961,7 @@
         <v>1424.1886696273727</v>
       </c>
       <c r="B318">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
@@ -2969,7 +2969,7 @@
         <v>1424.1886696273727</v>
       </c>
       <c r="B319">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
@@ -2977,7 +2977,7 @@
         <v>1434.6606451393388</v>
       </c>
       <c r="B320">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
@@ -2985,7 +2985,7 @@
         <v>1434.6606451393388</v>
       </c>
       <c r="B321">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
@@ -2993,7 +2993,7 @@
         <v>1445.1326206513047</v>
       </c>
       <c r="B322">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -3001,7 +3001,7 @@
         <v>1445.1326206513047</v>
       </c>
       <c r="B323">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -3009,7 +3009,7 @@
         <v>1455.6045961632708</v>
       </c>
       <c r="B324">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -3017,7 +3017,7 @@
         <v>1455.6045961632708</v>
       </c>
       <c r="B325">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -3025,7 +3025,7 @@
         <v>1466.0765716752367</v>
       </c>
       <c r="B326">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
@@ -3033,7 +3033,7 @@
         <v>1466.0765716752367</v>
       </c>
       <c r="B327">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
@@ -3041,7 +3041,7 @@
         <v>1476.5485471872028</v>
       </c>
       <c r="B328">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -3049,7 +3049,7 @@
         <v>1476.5485471872028</v>
       </c>
       <c r="B329">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -3057,7 +3057,7 @@
         <v>1487.0205226991686</v>
       </c>
       <c r="B330">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -3065,7 +3065,7 @@
         <v>1497.4924982111347</v>
       </c>
       <c r="B331">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -3073,7 +3073,7 @@
         <v>1497.4924982111347</v>
       </c>
       <c r="B332">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -3081,7 +3081,7 @@
         <v>1497.4924982111347</v>
       </c>
       <c r="B333">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
@@ -3089,7 +3089,7 @@
         <v>1507.9644737231006</v>
       </c>
       <c r="B334">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
@@ -3097,7 +3097,7 @@
         <v>1507.9644737231006</v>
       </c>
       <c r="B335">
-        <v>31.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
@@ -3105,7 +3105,7 @@
         <v>1518.4364492350667</v>
       </c>
       <c r="B336">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
@@ -3113,7 +3113,7 @@
         <v>1528.9084247470325</v>
       </c>
       <c r="B337">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
@@ -3121,7 +3121,7 @@
         <v>1539.3804002589986</v>
       </c>
       <c r="B338">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
@@ -3129,7 +3129,7 @@
         <v>1539.3804002589986</v>
       </c>
       <c r="B339">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
@@ -3137,7 +3137,7 @@
         <v>1539.3804002589986</v>
       </c>
       <c r="B340">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
@@ -3145,7 +3145,7 @@
         <v>1549.8523757709645</v>
       </c>
       <c r="B341">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
@@ -3153,7 +3153,7 @@
         <v>1549.8523757709645</v>
       </c>
       <c r="B342">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
@@ -3161,7 +3161,7 @@
         <v>1549.8523757709645</v>
       </c>
       <c r="B343">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
@@ -3169,7 +3169,7 @@
         <v>1549.8523757709645</v>
       </c>
       <c r="B344">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
@@ -3177,7 +3177,7 @@
         <v>1560.3243512829306</v>
       </c>
       <c r="B345">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
@@ -3185,7 +3185,7 @@
         <v>1560.3243512829306</v>
       </c>
       <c r="B346">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
@@ -3193,7 +3193,7 @@
         <v>1570.7963267948965</v>
       </c>
       <c r="B347">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
@@ -3201,7 +3201,7 @@
         <v>1570.7963267948965</v>
       </c>
       <c r="B348">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
@@ -3209,7 +3209,7 @@
         <v>1570.7963267948965</v>
       </c>
       <c r="B349">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
@@ -3217,7 +3217,7 @@
         <v>1570.7963267948965</v>
       </c>
       <c r="B350">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
@@ -3225,7 +3225,7 @@
         <v>1581.2683023068626</v>
       </c>
       <c r="B351">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
@@ -3233,7 +3233,7 @@
         <v>1581.2683023068626</v>
       </c>
       <c r="B352">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
@@ -3241,7 +3241,7 @@
         <v>1581.2683023068626</v>
       </c>
       <c r="B353">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
@@ -3249,7 +3249,7 @@
         <v>1591.7402778188284</v>
       </c>
       <c r="B354">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
@@ -3257,7 +3257,7 @@
         <v>1591.7402778188284</v>
       </c>
       <c r="B355">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
@@ -3265,7 +3265,7 @@
         <v>1602.2122533307945</v>
       </c>
       <c r="B356">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
@@ -3273,7 +3273,7 @@
         <v>1602.2122533307945</v>
       </c>
       <c r="B357">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
@@ -3281,7 +3281,7 @@
         <v>1602.2122533307945</v>
       </c>
       <c r="B358">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
@@ -3289,7 +3289,7 @@
         <v>1612.6842288427604</v>
       </c>
       <c r="B359">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
@@ -3297,7 +3297,7 @@
         <v>1612.6842288427604</v>
       </c>
       <c r="B360">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
@@ -3305,7 +3305,7 @@
         <v>1623.1562043547265</v>
       </c>
       <c r="B361">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
@@ -3313,7 +3313,7 @@
         <v>1623.1562043547265</v>
       </c>
       <c r="B362">
-        <v>27.6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
@@ -3321,7 +3321,7 @@
         <v>1623.1562043547265</v>
       </c>
       <c r="B363">
-        <v>27.6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
@@ -3329,7 +3329,7 @@
         <v>1623.1562043547265</v>
       </c>
       <c r="B364">
-        <v>27.4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
@@ -3337,7 +3337,7 @@
         <v>1623.1562043547265</v>
       </c>
       <c r="B365">
-        <v>27.4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
@@ -3345,7 +3345,7 @@
         <v>1633.6281798666923</v>
       </c>
       <c r="B366">
-        <v>27.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
@@ -3353,7 +3353,7 @@
         <v>1633.6281798666923</v>
       </c>
       <c r="B367">
-        <v>27.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
@@ -3361,15 +3361,12 @@
         <v>1633.6281798666923</v>
       </c>
       <c r="B368">
-        <v>27.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>1633.6281798666923</v>
-      </c>
-      <c r="B369">
-        <v>27</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
